--- a/data/wfa_sector_aggregate_2024-10-21_2026-04-20.xlsx
+++ b/data/wfa_sector_aggregate_2024-10-21_2026-04-20.xlsx
@@ -8,7 +8,7 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="a7d6480a-05cd-45ec-87c5-b9705c7" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="c4556edc-d98f-437e-b39e-e417bbe" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -335,19 +335,19 @@
         <v>10</v>
       </c>
       <c r="E2" s="0" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="F2" s="0" t="n">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="G2" s="0" t="n">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="H2" s="0" t="n">
-        <v>66.6666666666667</v>
+        <v>71.4285714285714</v>
       </c>
       <c r="I2" s="0" t="n">
-        <v>70.2380952380952</v>
+        <v>76.6666666666667</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -390,22 +390,22 @@
         <v>15</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F4" s="0" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G4" s="0" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H4" s="0" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="I4" s="0" t="n">
-        <v>0</v>
+        <v>64.7435897435897</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -422,19 +422,19 @@
         <v>10</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F5" s="0" t="n">
-        <v>52</v>
+        <v>20</v>
       </c>
       <c r="G5" s="0" t="n">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="H5" s="0" t="n">
-        <v>51.9230769230769</v>
+        <v>40</v>
       </c>
       <c r="I5" s="0" t="n">
-        <v>61.6666666666667</v>
+        <v>44.4444444444444</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -480,19 +480,19 @@
         <v>10</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F7" s="0" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G7" s="0" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H7" s="0" t="n">
-        <v>38.2352941176471</v>
+        <v>51.5151515151515</v>
       </c>
       <c r="I7" s="0" t="n">
-        <v>38.6666666666667</v>
+        <v>57.8947368421053</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -509,19 +509,19 @@
         <v>10</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="F8" s="0" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="G8" s="0" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="H8" s="0" t="n">
-        <v>60</v>
+        <v>57.1428571428571</v>
       </c>
       <c r="I8" s="0" t="n">
-        <v>66.0714285714286</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -564,22 +564,22 @@
         <v>15</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F10" s="0" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G10" s="0" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H10" s="0" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I10" s="0" t="n">
-        <v>0</v>
+        <v>57.1428571428571</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -596,19 +596,19 @@
         <v>10</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F11" s="0" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="G11" s="0" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="H11" s="0" t="n">
-        <v>54.1666666666667</v>
+        <v>50</v>
       </c>
       <c r="I11" s="0" t="n">
-        <v>59.2592592592593</v>
+        <v>56.6666666666667</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -654,19 +654,19 @@
         <v>10</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F13" s="0" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="G13" s="0" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="H13" s="0" t="n">
-        <v>47.0588235294118</v>
+        <v>34.6153846153846</v>
       </c>
       <c r="I13" s="0" t="n">
-        <v>47.5</v>
+        <v>35.1190476190476</v>
       </c>
     </row>
   </sheetData>
